--- a/src/assets/invoice_template.xlsx
+++ b/src/assets/invoice_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HYUNJU_RYU\dev\smart-invoice\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A613549B-9C24-405C-B321-FF574B73CEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F3A6B4-7DED-47C1-83A7-3F741D4A0858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20865" yWindow="1140" windowWidth="21600" windowHeight="11295" xr2:uid="{8EA528CF-440F-4A42-A7F1-3323D257DF6E}"/>
+    <workbookView xWindow="28680" yWindow="1050" windowWidth="29040" windowHeight="15720" xr2:uid="{8EA528CF-440F-4A42-A7F1-3323D257DF6E}"/>
   </bookViews>
   <sheets>
     <sheet name="合計請求明細書鑑" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="178" formatCode="@&quot;　御中&quot;"/>
+    <numFmt numFmtId="177" formatCode="@&quot;　御中&quot;"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -509,10 +509,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,48 +551,142 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>267591</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>13869</xdr:rowOff>
+      <xdr:rowOff>151572</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A2B4767-1CE2-530B-EDB1-05B565CD30B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E53EC576-993D-4E80-B0AE-8239683E46A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5334000" y="1600200"/>
-          <a:ext cx="2563116" cy="1537869"/>
+          <a:off x="5153025" y="1447800"/>
+          <a:ext cx="2838451" cy="1827972"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
+            <a:t>株式会社ソルエムジャパン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>〒</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>105-0021</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>東京都港区東新橋</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2-3-14</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>エディフィチオトーコー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>階</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>TEL 03-5273-3538</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>FAX 03-6273-3539</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>登録番号：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>T2010401174530</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -622,7 +716,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4334,15 +4428,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bb9526b-221f-43e7-a9ca-c97ff66af0d6">
@@ -4351,6 +4436,15 @@
     <TaxCatchAll xmlns="0d2ed01c-d650-4e80-8773-04905e47c66a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4373,14 +4467,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2ED7F77-F12D-4F2A-B958-2CE47797289F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{201B0B37-B479-42F4-BEDA-C85FCD3FF85C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4389,4 +4475,18 @@
     <ds:schemaRef ds:uri="0d2ed01c-d650-4e80-8773-04905e47c66a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2ED7F77-F12D-4F2A-B958-2CE47797289F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{44742336-914c-47dd-9668-37ab4b821de8}" enabled="1" method="Standard" siteId="{3489ac63-3ba9-41fb-8dbd-c0d8992b46b0}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/src/assets/invoice_template.xlsx
+++ b/src/assets/invoice_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HYUNJU_RYU\dev\smart-invoice\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F3A6B4-7DED-47C1-83A7-3F741D4A0858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B794F-7630-4251-8178-9B1A4E5DFB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1050" windowWidth="29040" windowHeight="15720" xr2:uid="{8EA528CF-440F-4A42-A7F1-3323D257DF6E}"/>
   </bookViews>
@@ -551,142 +551,55 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>314325</xdr:rowOff>
+      <xdr:colOff>219076</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>295276</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>151572</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E53EC576-993D-4E80-B0AE-8239683E46A2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{718414CC-D5EF-3CA9-4D38-D590B3C69A80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect r="8781" b="14063"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5153025" y="1447800"/>
-          <a:ext cx="2838451" cy="1827972"/>
+          <a:off x="5334001" y="1562100"/>
+          <a:ext cx="2590800" cy="1571625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1"/>
-            <a:t>株式会社ソルエムジャパン</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>〒</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>105-0021</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>東京都港区東新橋</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>2-3-14</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>エディフィチオトーコー </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>5</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>階</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>TEL 03-5273-3538</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>　　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>FAX 03-6273-3539</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>登録番号：</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>T2010401174530</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0">
-            <a:latin typeface="+mn-ea"/>
-            <a:ea typeface="+mn-ea"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -716,7 +629,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4428,6 +4341,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bb9526b-221f-43e7-a9ca-c97ff66af0d6">
@@ -4436,15 +4358,6 @@
     <TaxCatchAll xmlns="0d2ed01c-d650-4e80-8773-04905e47c66a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4467,6 +4380,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2ED7F77-F12D-4F2A-B958-2CE47797289F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{201B0B37-B479-42F4-BEDA-C85FCD3FF85C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4477,14 +4398,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2ED7F77-F12D-4F2A-B958-2CE47797289F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{44742336-914c-47dd-9668-37ab4b821de8}" enabled="1" method="Standard" siteId="{3489ac63-3ba9-41fb-8dbd-c0d8992b46b0}" contentBits="0" removed="0"/>
